--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260824.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260824.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.16%</t>
+          <t>10.12%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.76%</t>
+          <t>9.43%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.82%</t>
+          <t>7.83%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>6.95%</t>
         </is>
       </c>
     </row>
@@ -704,51 +704,51 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>6.00%</t>
+          <t>6.04%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>25,387,000</t>
+          <t>2,226,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.99%</t>
+          <t>5.03%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2,226,000</t>
+          <t>25,387,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.94%</t>
+          <t>5.02%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.82%</t>
+          <t>4.96%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.74%</t>
+          <t>4.87%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,395,000</t>
+          <t>2,407,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.45%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>4.37%</t>
+          <t>4.38%</t>
         </is>
       </c>
     </row>
@@ -858,73 +858,73 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>4.14%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>9,624,000</t>
+          <t>89,518,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>3.97%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>4,671,848</t>
+          <t>9,624,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>3.92%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>87,518,000</t>
+          <t>4,671,848</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.44%</t>
         </is>
       </c>
     </row>
@@ -946,51 +946,51 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>202609TX</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>台指期貨</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>410,900</t>
+          <t>679</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>202609TX</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台指期貨</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>383,900</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1085,110 +1085,110 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2,424,000</t>
+          <t>1,301,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>477,000</t>
+          <t>255,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>1,101,000</t>
+          <t>2,424,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>5,917,000</t>
+          <t>477,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>142,000</t>
+          <t>5,917,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1217,44 +1217,44 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>3,249,000</t>
+          <t>483,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>483,000</t>
+          <t>3,249,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
@@ -1371,34 +1371,34 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>8,130,177,759</t>
+          <t>2,492,961,604</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,761,610,138</t>
+          <t>1,707,561,738</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1769,10 +1769,28 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>684,666,445</t>
+          <t>-106,270,174</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>RP_NTD</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>RP</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>3,266,182,664</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
